--- a/artfynd/A 38681-2021 artfynd.xlsx
+++ b/artfynd/A 38681-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,47 +675,38 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120507017</v>
+        <v>120507051</v>
       </c>
       <c r="B2" t="n">
-        <v>57501</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5173</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>102185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Myskbock</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Aromia moschata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>750657</v>
+        <v>750731</v>
       </c>
       <c r="R2" t="n">
-        <v>7089918</v>
+        <v>7089867</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -771,6 +762,11 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
@@ -783,6 +779,112 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>120507017</v>
+      </c>
+      <c r="B3" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Strandpromenaden, Kåddis, Vb</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>750657</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7089918</v>
+      </c>
+      <c r="S3" t="n">
+        <v>50</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
